--- a/planilha/planilha-artgenmediarats.xlsx
+++ b/planilha/planilha-artgenmediarats.xlsx
@@ -866,7 +866,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>06/04/2026 15:04</t>
+          <t>06/04/2026 15:43</t>
         </is>
       </c>
     </row>

--- a/planilha/planilha-artgenmediarats.xlsx
+++ b/planilha/planilha-artgenmediarats.xlsx
@@ -65,7 +65,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -132,6 +132,18 @@
         <bgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9C4"/>
+        <bgColor rgb="00FFF9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -160,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -195,6 +207,10 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -562,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="12" min="1" max="1"/>
@@ -592,6 +608,51 @@
           <t>OBSERVACOES</t>
         </is>
       </c>
+      <c r="E1" s="18" t="inlineStr">
+        <is>
+          <t>NICHO</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>DESCRICAO</t>
+        </is>
+      </c>
+      <c r="G1" s="18" t="inlineStr">
+        <is>
+          <t>PUBLICO_ALVO</t>
+        </is>
+      </c>
+      <c r="H1" s="18" t="inlineStr">
+        <is>
+          <t>FORMALIDADE</t>
+        </is>
+      </c>
+      <c r="I1" s="18" t="inlineStr">
+        <is>
+          <t>ESTILO_VISUAL</t>
+        </is>
+      </c>
+      <c r="J1" s="18" t="inlineStr">
+        <is>
+          <t>ESTILO_FOTO</t>
+        </is>
+      </c>
+      <c r="K1" s="18" t="inlineStr">
+        <is>
+          <t>COR_PRIMARIA</t>
+        </is>
+      </c>
+      <c r="L1" s="18" t="inlineStr">
+        <is>
+          <t>COR_SECUNDARIA</t>
+        </is>
+      </c>
+      <c r="M1" s="18" t="inlineStr">
+        <is>
+          <t>COR_FUNDO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
@@ -601,7 +662,7 @@
       </c>
       <c r="B2" s="16" t="inlineStr">
         <is>
-          <t>Dude Brand</t>
+          <t>DudeCamp</t>
         </is>
       </c>
       <c r="C2" s="16" t="inlineStr">
@@ -614,44 +675,44 @@
           <t>Cliente exemplo</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>MR</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>Media Rats</t>
-        </is>
-      </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>hello@mediarats.com</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>Cliente interno</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>TEST</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Teste Co</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr"/>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>Dados de teste</t>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Educação Tech</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>DudeCamp é um curso online divertido e prático de HTML + CSS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>16 - 50 anos, aprender programação web.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Técnico, Descontraído.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>#050505</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>#F5C400</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>#050505</t>
         </is>
       </c>
     </row>
@@ -666,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="12" min="1" max="1"/>
@@ -804,9 +865,9 @@
           <t>Lançamento de Verão</t>
         </is>
       </c>
-      <c r="F2" s="19" t="inlineStr">
-        <is>
-          <t>Gerado</t>
+      <c r="F2" s="21" t="inlineStr">
+        <is>
+          <t>Cancelado</t>
         </is>
       </c>
       <c r="G2" s="16" t="inlineStr">
@@ -866,7 +927,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>06/04/2026 15:43</t>
+          <t>06/04/2026 16:47</t>
         </is>
       </c>
     </row>
@@ -894,9 +955,9 @@
           <t>Identidade Visual</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t>Cancelado</t>
         </is>
       </c>
       <c r="G3" s="16" t="inlineStr">
@@ -952,6 +1013,46 @@
       <c r="Q3" s="16" t="inlineStr">
         <is>
           <t>Foto estilo editorial de mesa de trabalho criativa com notebook, câmera, caderno e café</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DUDE#2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DUDE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DudeCamp</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Blackfriday</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>Planejado</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Arte Tech</t>
         </is>
       </c>
     </row>

--- a/planilha/planilha-artgenmediarats.xlsx
+++ b/planilha/planilha-artgenmediarats.xlsx
@@ -172,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -213,6 +213,8 @@
     <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -727,7 +729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="12" min="1" max="1"/>
@@ -1040,9 +1042,9 @@
           <t>Blackfriday</t>
         </is>
       </c>
-      <c r="F4" s="20" t="inlineStr">
-        <is>
-          <t>Planejado</t>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>Cancelado</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1053,6 +1055,61 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>Arte Tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DUDE#3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DUDE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DudeCamp</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>Gerado</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante, elementos de código flutuante como partículas, laptop moderno no centro exibindo página web responsiva animada, texto principal em negrito branco com glow "Domine CSS: Crie designs incríveis e responsivos!", subtítulo "Aprenda flexbox, grid e animações hoje" em fonte moderna, estilo cyberpunk minimalista, alta resolução para Instagram.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante com toques verde neon, elementos de código flutuante como partículas organizando caixas flexíveis, laptop moderno no centro exibindo layout responsivo com flexbox, texto principal em negrito branco com glow verde "Domine CSS Flexbox: Layouts perfeitos em minutos!", subtítulo "Controle alinhamento e espaçamento como um pro" em fonte moderna, estilo tech futurista, alta resolução para Instagram.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante com explosões laranja flamejante, elementos de código flutuante como @keyframes explodindo, laptop moderno no centro exibindo UI animada suave, texto principal em negrito branco com glow laranja pulsante "Domine CSS Animações: Dê vida ao seu site!", subtítulo "Transições fluidas sem JavaScript" em fonte moderna, estilo dinâmico moderno, alta resolução para Instagram.</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>09/04/2026 15:32</t>
         </is>
       </c>
     </row>

--- a/planilha/planilha-artgenmediarats.xlsx
+++ b/planilha/planilha-artgenmediarats.xlsx
@@ -729,7 +729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="12" min="1" max="1"/>
@@ -844,272 +844,57 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>DUDE#1</t>
         </is>
       </c>
-      <c r="B2" s="16" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>DUDE</t>
         </is>
       </c>
-      <c r="C2" s="16" t="inlineStr">
-        <is>
-          <t>Dude Brand</t>
-        </is>
-      </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DudeCamp</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="16" t="inlineStr">
-        <is>
-          <t>Lançamento de Verão</t>
-        </is>
-      </c>
-      <c r="F2" s="21" t="inlineStr">
-        <is>
-          <t>Cancelado</t>
-        </is>
-      </c>
-      <c r="G2" s="16" t="inlineStr">
-        <is>
-          <t>30/04/2025</t>
-        </is>
-      </c>
-      <c r="H2" s="16" t="inlineStr">
-        <is>
-          <t>Cena de praia tropical ao entardecer com produto de bebida energética em destaque, estilo fotografia comercial vibrante</t>
-        </is>
-      </c>
-      <c r="I2" s="16" t="inlineStr">
-        <is>
-          <t>Jovens surfistas celebrando vitória na praia, logotipo Dude Brand visível, paleta de cores azul e laranja</t>
-        </is>
-      </c>
-      <c r="J2" s="16" t="inlineStr">
-        <is>
-          <t>Produto Dude Energy colocado em areia molhada com ondas ao fundo, efeito bokeh suave, cores quentes</t>
-        </is>
-      </c>
-      <c r="K2" s="16" t="inlineStr">
-        <is>
-          <t>Flat lay de produtos de verão: óculos, protetor solar, produto Dude Brand, fundo de madeira rústica</t>
-        </is>
-      </c>
-      <c r="L2" s="16" t="inlineStr">
-        <is>
-          <t>Homem atlético correndo na praia ao amanhecer, silhueta contra céu colorido, marca discreta no canto</t>
-        </is>
-      </c>
-      <c r="M2" s="16" t="inlineStr">
-        <is>
-          <t>Coquetéis tropicais com lata Dude Brand, fundo de folhagens exóticas, estilo editorial de moda</t>
-        </is>
-      </c>
-      <c r="N2" s="16" t="inlineStr">
-        <is>
-          <t>Vista aérea de piscina luxuosa com flutuadores coloridos e produto Dude visível, estilo lifestyle</t>
-        </is>
-      </c>
-      <c r="O2" s="16" t="inlineStr">
-        <is>
-          <t>Casal jovem tomando Dude Energy ao pôr do sol na varanda com vista para o oceano</t>
-        </is>
-      </c>
-      <c r="P2" s="16" t="inlineStr">
-        <is>
-          <t>Detalhe macro da lata Dude Brand com gotas de água, fundo desfocado de praia, alta qualidade</t>
-        </is>
-      </c>
-      <c r="Q2" s="16" t="inlineStr">
-        <is>
-          <t>Festival de música ao ar livre com bandeiras Dude Brand, público animado, iluminação colorida noturna</t>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="F2" s="23" t="inlineStr">
+        <is>
+          <t>Gerado</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante, elementos de código flutuante como partículas, laptop moderno no centro exibindo página web responsiva animada, texto principal em negrito branco com glow "Domine CSS: Crie designs incríveis e responsivos!", subtítulo "Aprenda flexbox, grid e animações hoje" em fonte moderna, estilo cyberpunk minimalista, alta resolução para Instagram.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante com toques verde neon, elementos de código flutuante como partículas organizando caixas flexíveis, laptop moderno no centro exibindo layout responsivo com flexbox, texto principal em negrito branco com glow verde "Domine CSS Flexbox: Layouts perfeitos em minutos!", subtítulo "Controle alinhamento e espaçamento como um pro" em fonte moderna, estilo tech futurista, alta resolução para Instagram.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante com explosões laranja flamejante, elementos de código flutuante como @keyframes explodindo, laptop moderno no centro exibindo UI animada suave, texto principal em negrito branco com glow laranja pulsante "Domine CSS Animações: Dê vida ao seu site!", subtítulo "Transições fluidas sem JavaScript" em fonte moderna, estilo dinâmico moderno, alta resolução para Instagram.</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>06/04/2026 16:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="16" t="inlineStr">
-        <is>
-          <t>MR#1</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>MR</t>
-        </is>
-      </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>Media Rats</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>Identidade Visual</t>
-        </is>
-      </c>
-      <c r="F3" s="21" t="inlineStr">
-        <is>
-          <t>Cancelado</t>
-        </is>
-      </c>
-      <c r="G3" s="16" t="inlineStr">
-        <is>
-          <t>05/05/2025</t>
-        </is>
-      </c>
-      <c r="H3" s="16" t="inlineStr">
-        <is>
-          <t>Logo Media Rats em estilo cyberpunk com rato geométrico neon em fundo preto, design moderno</t>
-        </is>
-      </c>
-      <c r="I3" s="16" t="inlineStr">
-        <is>
-          <t>Escritório criativo futurista com telas holográficas mostrando dados de mídia social, equipe diversa</t>
-        </is>
-      </c>
-      <c r="J3" s="16" t="inlineStr">
-        <is>
-          <t>Mockup de smartphone com interface de dashboard de analytics colorida, fundo gradiente roxo</t>
-        </is>
-      </c>
-      <c r="K3" s="16" t="inlineStr">
-        <is>
-          <t>Ícone de rato vetorial minimalista em gradiente azul e roxo para uso em redes sociais</t>
-        </is>
-      </c>
-      <c r="L3" s="16" t="inlineStr">
-        <is>
-          <t>Banner para LinkedIn com texto 'Media Rats - Criatividade Que Converte', fundo escuro profissional</t>
-        </is>
-      </c>
-      <c r="M3" s="16" t="inlineStr">
-        <is>
-          <t>Colagem artística de elementos de marketing digital: gráficos, trends, emojis, fundo branco</t>
-        </is>
-      </c>
-      <c r="N3" s="16" t="inlineStr">
-        <is>
-          <t>Mascote rato animado segurando tablet com gráficos de crescimento, estilo cartoon moderno</t>
-        </is>
-      </c>
-      <c r="O3" s="16" t="inlineStr">
-        <is>
-          <t>Story do Instagram com paleta de cores da marca, tipografia bold, call-to-action vibrante</t>
-        </is>
-      </c>
-      <c r="P3" s="16" t="inlineStr">
-        <is>
-          <t>Apresentação de pitch com slides escuros, dados de resultado de campanha, visual executivo</t>
-        </is>
-      </c>
-      <c r="Q3" s="16" t="inlineStr">
-        <is>
-          <t>Foto estilo editorial de mesa de trabalho criativa com notebook, câmera, caderno e café</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DUDE#2</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DUDE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>DudeCamp</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Blackfriday</t>
-        </is>
-      </c>
-      <c r="F4" s="22" t="inlineStr">
-        <is>
-          <t>Cancelado</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Arte Tech</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DUDE#3</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>DUDE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>DudeCamp</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="F5" s="23" t="inlineStr">
-        <is>
-          <t>Gerado</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante, elementos de código flutuante como partículas, laptop moderno no centro exibindo página web responsiva animada, texto principal em negrito branco com glow "Domine CSS: Crie designs incríveis e responsivos!", subtítulo "Aprenda flexbox, grid e animações hoje" em fonte moderna, estilo cyberpunk minimalista, alta resolução para Instagram.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante com toques verde neon, elementos de código flutuante como partículas organizando caixas flexíveis, laptop moderno no centro exibindo layout responsivo com flexbox, texto principal em negrito branco com glow verde "Domine CSS Flexbox: Layouts perfeitos em minutos!", subtítulo "Controle alinhamento e espaçamento como um pro" em fonte moderna, estilo tech futurista, alta resolução para Instagram.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante com explosões laranja flamejante, elementos de código flutuante como @keyframes explodindo, laptop moderno no centro exibindo UI animada suave, texto principal em negrito branco com glow laranja pulsante "Domine CSS Animações: Dê vida ao seu site!", subtítulo "Transições fluidas sem JavaScript" em fonte moderna, estilo dinâmico moderno, alta resolução para Instagram.</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>09/04/2026 15:32</t>
+          <t>09/04/2026 15:57</t>
         </is>
       </c>
     </row>

--- a/planilha/planilha-artgenmediarats.xlsx
+++ b/planilha/planilha-artgenmediarats.xlsx
@@ -867,9 +867,9 @@
           <t>CSS</t>
         </is>
       </c>
-      <c r="F2" s="23" t="inlineStr">
-        <is>
-          <t>Gerado</t>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>Planejado</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -885,16 +885,6 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante com toques verde neon, elementos de código flutuante como partículas organizando caixas flexíveis, laptop moderno no centro exibindo layout responsivo com flexbox, texto principal em negrito branco com glow verde "Domine CSS Flexbox: Layouts perfeitos em minutos!", subtítulo "Controle alinhamento e espaçamento como um pro" em fonte moderna, estilo tech futurista, alta resolução para Instagram.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante com explosões laranja flamejante, elementos de código flutuante como @keyframes explodindo, laptop moderno no centro exibindo UI animada suave, texto principal em negrito branco com glow laranja pulsante "Domine CSS Animações: Dê vida ao seu site!", subtítulo "Transições fluidas sem JavaScript" em fonte moderna, estilo dinâmico moderno, alta resolução para Instagram.</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>09/04/2026 15:57</t>
         </is>
       </c>
     </row>

--- a/planilha/planilha-artgenmediarats.xlsx
+++ b/planilha/planilha-artgenmediarats.xlsx
@@ -867,9 +867,9 @@
           <t>CSS</t>
         </is>
       </c>
-      <c r="F2" s="20" t="inlineStr">
-        <is>
-          <t>Planejado</t>
+      <c r="F2" s="23" t="inlineStr">
+        <is>
+          <t>Gerado</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -885,6 +885,11 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante com toques verde neon, elementos de código flutuante como partículas organizando caixas flexíveis, laptop moderno no centro exibindo layout responsivo com flexbox, texto principal em negrito branco com glow verde "Domine CSS Flexbox: Layouts perfeitos em minutos!", subtítulo "Controle alinhamento e espaçamento como um pro" em fonte moderna, estilo tech futurista, alta resolução para Instagram.</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>09/04/2026 16:59</t>
         </is>
       </c>
     </row>
@@ -899,7 +904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="12" min="1" max="1"/>
@@ -971,6 +976,84 @@
           <t>Proximas_Acoes</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DUDE#1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DudeCamp</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante, elementos de código flutuante como partículas, laptop moderno no centro exibindo página web responsiva animada, texto principal em negrito branco com glow "Domine CSS: Crie designs incríveis e responsivos!", subtítulo "Aprenda flexbox, grid e animações hoje" em fonte moderna, estilo cyberpunk minimalista, alta resolução para Instagram.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>DUDE_1\DUDE#1_001.jpg</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DUDE#1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DudeCamp</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante com toques verde neon, elementos de código flutuante como partículas organizando caixas flexíveis, laptop moderno no centro exibindo layout responsivo com flexbox, texto principal em negrito branco com glow verde "Domine CSS Flexbox: Layouts perfeitos em minutos!", subtítulo "Controle alinhamento e espaçamento como um pro" em fonte moderna, estilo tech futurista, alta resolução para Instagram.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>DUDE_1\DUDE#1_002.jpg</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/planilha/planilha-artgenmediarats.xlsx
+++ b/planilha/planilha-artgenmediarats.xlsx
@@ -887,9 +887,14 @@
           <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante com toques verde neon, elementos de código flutuante como partículas organizando caixas flexíveis, laptop moderno no centro exibindo layout responsivo com flexbox, texto principal em negrito branco com glow verde "Domine CSS Flexbox: Layouts perfeitos em minutos!", subtítulo "Controle alinhamento e espaçamento como um pro" em fonte moderna, estilo tech futurista, alta resolução para Instagram.</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante com explosões laranja flamejante, elementos de código flutuante como @keyframes explodindo, laptop moderno no centro exibindo UI animada suave, texto principal em negrito branco com glow laranja pulsante "Domine CSS Animações: Dê vida ao seu site!", subtítulo "Transições fluidas sem JavaScript" em fonte moderna, estilo dinâmico moderno, alta resolução para Instagram.</t>
+        </is>
+      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>09/04/2026 16:59</t>
+          <t>09/04/2026 18:41</t>
         </is>
       </c>
     </row>
@@ -904,7 +909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="12" min="1" max="1"/>
@@ -1006,15 +1011,11 @@
           <t>DUDE_1\DUDE#1_001.jpg</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1045,15 +1046,128 @@
           <t>DUDE_1\DUDE#1_002.jpg</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DUDE#1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DudeCamp</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante, elementos de código flutuante como partículas, laptop moderno no centro exibindo página web responsiva animada, texto principal em negrito branco com glow "Domine CSS: Crie designs incríveis e responsivos!", subtítulo "Aprenda flexbox, grid e animações hoje" em fonte moderna, estilo cyberpunk minimalista, alta resolução para Instagram.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>DUDE_1\DUDE#1_001.jpg</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DUDE#1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DudeCamp</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante com toques verde neon, elementos de código flutuante como partículas organizando caixas flexíveis, laptop moderno no centro exibindo layout responsivo com flexbox, texto principal em negrito branco com glow verde "Domine CSS Flexbox: Layouts perfeitos em minutos!", subtítulo "Controle alinhamento e espaçamento como um pro" em fonte moderna, estilo tech futurista, alta resolução para Instagram.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>DUDE_1\DUDE#1_002.jpg</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DUDE#1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DudeCamp</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante com explosões laranja flamejante, elementos de código flutuante como @keyframes explodindo, laptop moderno no centro exibindo UI animada suave, texto principal em negrito branco com glow laranja pulsante "Domine CSS Animações: Dê vida ao seu site!", subtítulo "Transições fluidas sem JavaScript" em fonte moderna, estilo dinâmico moderno, alta resolução para Instagram.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>DUDE_1\DUDE#1_003.jpg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/planilha/planilha-artgenmediarats.xlsx
+++ b/planilha/planilha-artgenmediarats.xlsx
@@ -894,7 +894,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>09/04/2026 18:41</t>
+          <t>10/04/2026 13:58</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="12" min="1" max="1"/>
@@ -1081,15 +1081,11 @@
           <t>DUDE_1\DUDE#1_001.jpg</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1120,15 +1116,11 @@
           <t>DUDE_1\DUDE#1_002.jpg</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1159,15 +1151,163 @@
           <t>DUDE_1\DUDE#1_003.jpg</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DUDE#1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DudeCamp</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante, elementos de código flutuante como partículas, laptop moderno no centro exibindo página web responsiva animada, texto principal em negrito branco com glow "Domine CSS: Crie designs incríveis e responsivos!", subtítulo "Aprenda flexbox, grid e animações hoje" em fonte moderna, estilo cyberpunk minimalista, alta resolução para Instagram.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>DUDE_1\DUDE#1_001.jpg</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DUDE#1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DudeCamp</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante, elementos de código flutuante como partículas, laptop moderno no centro exibindo página web responsiva animada, texto principal em negrito branco com glow "Domine CSS: Crie designs incríveis e responsivos!", subtítulo "Aprenda flexbox, grid e animações hoje" em fonte moderna, estilo cyberpunk minimalista, alta resolução para Instagram.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>DUDE_1\DUDE#1_001.jpg</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DUDE#1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DudeCamp</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante com toques verde neon, elementos de código flutuante como partículas organizando caixas flexíveis, laptop moderno no centro exibindo layout responsivo com flexbox, texto principal em negrito branco com glow verde "Domine CSS Flexbox: Layouts perfeitos em minutos!", subtítulo "Controle alinhamento e espaçamento como um pro" em fonte moderna, estilo tech futurista, alta resolução para Instagram.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>DUDE_1\DUDE#1_002.jpg</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DUDE#1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DudeCamp</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante com explosões laranja flamejante, elementos de código flutuante como @keyframes explodindo, laptop moderno no centro exibindo UI animada suave, texto principal em negrito branco com glow laranja pulsante "Domine CSS Animações: Dê vida ao seu site!", subtítulo "Transições fluidas sem JavaScript" em fonte moderna, estilo dinâmico moderno, alta resolução para Instagram.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>DUDE_1\DUDE#1_003.jpg</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/planilha/planilha-artgenmediarats.xlsx
+++ b/planilha/planilha-artgenmediarats.xlsx
@@ -894,7 +894,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>10/04/2026 13:58</t>
+          <t>10/04/2026 22:09</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="12" min="1" max="1"/>
@@ -1221,15 +1221,11 @@
           <t>DUDE_1\DUDE#1_001.jpg</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1260,15 +1256,11 @@
           <t>DUDE_1\DUDE#1_002.jpg</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1299,15 +1291,116 @@
           <t>DUDE_1\DUDE#1_003.jpg</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DUDE#1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DudeCamp</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante, elementos de código flutuante como partículas, laptop moderno no centro exibindo página web responsiva animada, texto principal em negrito branco com glow "Domine CSS: Crie designs incríveis e responsivos!", subtítulo "Aprenda flexbox, grid e animações hoje" em fonte moderna, estilo cyberpunk minimalista, alta resolução para Instagram.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>DUDE_1\DUDE#1_001.jpg</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DUDE#1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DudeCamp</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante com toques verde neon, elementos de código flutuante como partículas organizando caixas flexíveis, laptop moderno no centro exibindo layout responsivo com flexbox, texto principal em negrito branco com glow verde "Domine CSS Flexbox: Layouts perfeitos em minutos!", subtítulo "Controle alinhamento e espaçamento como um pro" em fonte moderna, estilo tech futurista, alta resolução para Instagram.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>DUDE_1\DUDE#1_002.jpg</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DUDE#1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>DudeCamp</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Crie uma arte impactante para post de redes sociais sobre CSS: fundo gradiente azul escuro para roxo vibrante com explosões laranja flamejante, elementos de código flutuante como @keyframes explodindo, laptop moderno no centro exibindo UI animada suave, texto principal em negrito branco com glow laranja pulsante "Domine CSS Animações: Dê vida ao seu site!", subtítulo "Transições fluidas sem JavaScript" em fonte moderna, estilo dinâmico moderno, alta resolução para Instagram.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>DUDE_1\DUDE#1_003.jpg</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/planilha/planilha-artgenmediarats.xlsx
+++ b/planilha/planilha-artgenmediarats.xlsx
@@ -894,7 +894,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>10/04/2026 22:09</t>
+          <t>11/04/2026 00:47</t>
         </is>
       </c>
     </row>
